--- a/data/dividends_info_20260320.xlsx
+++ b/data/dividends_info_20260320.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>51.29999923706055</v>
+        <v>50.34999847412109</v>
       </c>
       <c r="I2" t="n">
-        <v>1.364522437447329</v>
+        <v>1.390268165270722</v>
       </c>
       <c r="J2" t="n">
         <v>339</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.945999979972839</v>
+        <v>1.96399998664856</v>
       </c>
       <c r="I3" t="n">
-        <v>3.956834573095664</v>
+        <v>3.920570291418157</v>
       </c>
       <c r="J3" t="n">
         <v>248</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5.5</v>
+        <v>5.389999866485596</v>
       </c>
       <c r="I4" t="n">
-        <v>3.636363636363637</v>
+        <v>3.710575231060341</v>
       </c>
       <c r="J4" t="n">
         <v>241</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>18.79999923706055</v>
+        <v>18.29999923706055</v>
       </c>
       <c r="I5" t="n">
-        <v>2.000000081163775</v>
+        <v>2.054644894402713</v>
       </c>
       <c r="J5" t="n">
         <v>122</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4.320000171661377</v>
+        <v>4.244999885559082</v>
       </c>
       <c r="I6" t="n">
-        <v>2.77777766739881</v>
+        <v>2.826855199884077</v>
       </c>
       <c r="J6" t="n">
         <v>115</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>31.54999923706055</v>
+        <v>30.60000038146973</v>
       </c>
       <c r="I8" t="n">
-        <v>0.475435827661767</v>
+        <v>0.4901960723204261</v>
       </c>
       <c r="J8" t="n">
         <v>108</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>22.02000045776367</v>
+        <v>21.73999977111816</v>
       </c>
       <c r="I9" t="n">
-        <v>1.135331493201021</v>
+        <v>1.149954013946807</v>
       </c>
       <c r="J9" t="n">
         <v>94</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>63.20000076293945</v>
+        <v>60.59999847412109</v>
       </c>
       <c r="I11" t="n">
-        <v>0.99683543100435</v>
+        <v>1.039603986572769</v>
       </c>
       <c r="J11" t="n">
         <v>94</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>21.46999931335449</v>
+        <v>21.45000076293945</v>
       </c>
       <c r="I12" t="n">
-        <v>3.959012702302668</v>
+        <v>3.962703821757432</v>
       </c>
       <c r="J12" t="n">
         <v>94</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.381999969482422</v>
+        <v>6.369999885559082</v>
       </c>
       <c r="I13" t="n">
-        <v>2.840802269930179</v>
+        <v>2.846153897286729</v>
       </c>
       <c r="J13" t="n">
         <v>94</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7.730000019073486</v>
+        <v>7.690000057220459</v>
       </c>
       <c r="I14" t="n">
-        <v>3.363518749786025</v>
+        <v>3.381014279133526</v>
       </c>
       <c r="J14" t="n">
         <v>94</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>26.14999961853027</v>
+        <v>25.85000038146973</v>
       </c>
       <c r="I15" t="n">
-        <v>4.244741935726217</v>
+        <v>4.294003805105127</v>
       </c>
       <c r="J15" t="n">
         <v>76</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.8209999799728394</v>
+        <v>0.8159999847412109</v>
       </c>
       <c r="I16" t="n">
-        <v>3.654080478904819</v>
+        <v>3.676470656983444</v>
       </c>
       <c r="J16" t="n">
         <v>73</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>11.63000011444092</v>
+        <v>11.5</v>
       </c>
       <c r="I17" t="n">
-        <v>2.149613048494953</v>
+        <v>2.173913043478261</v>
       </c>
       <c r="J17" t="n">
         <v>66</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3.559999942779541</v>
+        <v>3.539999961853027</v>
       </c>
       <c r="I18" t="n">
-        <v>4.213483213791417</v>
+        <v>4.237288181254157</v>
       </c>
       <c r="J18" t="n">
         <v>66</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.365000009536743</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="I19" t="n">
-        <v>4.397462984381617</v>
+        <v>4.444444607465701</v>
       </c>
       <c r="J19" t="n">
         <v>59</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>8.031999588012695</v>
+        <v>8.369999885559082</v>
       </c>
       <c r="I20" t="n">
-        <v>3.610557954121519</v>
+        <v>3.464755125031034</v>
       </c>
       <c r="J20" t="n">
         <v>59</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.945999979972839</v>
+        <v>1.96399998664856</v>
       </c>
       <c r="I21" t="n">
-        <v>3.956834573095664</v>
+        <v>3.920570291418157</v>
       </c>
       <c r="J21" t="n">
         <v>59</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>33.7599983215332</v>
+        <v>33.34999847412109</v>
       </c>
       <c r="I22" t="n">
-        <v>4.857820146732518</v>
+        <v>4.917541454379993</v>
       </c>
       <c r="J22" t="n">
         <v>59</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>32.33000183105469</v>
+        <v>31.68000030517578</v>
       </c>
       <c r="I23" t="n">
-        <v>6.186204413013344</v>
+        <v>6.313131252316453</v>
       </c>
       <c r="J23" t="n">
         <v>59</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3.624000072479248</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="I24" t="n">
-        <v>2.759381843267682</v>
+        <v>2.79329614891385</v>
       </c>
       <c r="J24" t="n">
         <v>59</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>37.5</v>
+        <v>35</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3958933333333334</v>
+        <v>0.4241714285714286</v>
       </c>
       <c r="J25" t="n">
         <v>59</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>22.05999946594238</v>
+        <v>21.79999923706055</v>
       </c>
       <c r="I26" t="n">
-        <v>4.170444343937333</v>
+        <v>4.220183633933238</v>
       </c>
       <c r="J26" t="n">
         <v>59</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>7.554999828338623</v>
+        <v>7.474999904632568</v>
       </c>
       <c r="I27" t="n">
-        <v>3.970880302004868</v>
+        <v>4.013377977624823</v>
       </c>
       <c r="J27" t="n">
         <v>59</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>74.18000030517578</v>
+        <v>72.33999633789062</v>
       </c>
       <c r="I28" t="n">
-        <v>1.401995141172082</v>
+        <v>1.437655588399945</v>
       </c>
       <c r="J28" t="n">
         <v>59</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>51.29999923706055</v>
+        <v>50.34999847412109</v>
       </c>
       <c r="I29" t="n">
-        <v>4.288499089120179</v>
+        <v>4.369414233707984</v>
       </c>
       <c r="J29" t="n">
         <v>59</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6.967000007629395</v>
+        <v>7.065000057220459</v>
       </c>
       <c r="I30" t="n">
-        <v>12.34390697657865</v>
+        <v>12.17268213778819</v>
       </c>
       <c r="J30" t="n">
         <v>59</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>10.72999954223633</v>
+        <v>10.46500015258789</v>
       </c>
       <c r="I31" t="n">
-        <v>5.219012338217545</v>
+        <v>5.35117049053762</v>
       </c>
       <c r="J31" t="n">
         <v>59</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1.784999966621399</v>
+        <v>1.754999995231628</v>
       </c>
       <c r="I32" t="n">
-        <v>2.240896400447051</v>
+        <v>2.279202285394919</v>
       </c>
       <c r="J32" t="n">
         <v>59</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>8.779999732971191</v>
+        <v>8.720000267028809</v>
       </c>
       <c r="I33" t="n">
-        <v>3.416856595945233</v>
+        <v>3.440366867124189</v>
       </c>
       <c r="J33" t="n">
         <v>59</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.299999952316284</v>
+        <v>2.289999961853027</v>
       </c>
       <c r="I34" t="n">
-        <v>4.695652271263543</v>
+        <v>4.716157283802238</v>
       </c>
       <c r="J34" t="n">
         <v>59</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>62</v>
+        <v>60.70000076293945</v>
       </c>
       <c r="I35" t="n">
-        <v>3.32258064516129</v>
+        <v>3.393739660803659</v>
       </c>
       <c r="J35" t="n">
         <v>59</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>14.27999973297119</v>
+        <v>14.07999992370605</v>
       </c>
       <c r="I36" t="n">
-        <v>5.252100938547777</v>
+        <v>5.326704574317849</v>
       </c>
       <c r="J36" t="n">
         <v>59</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>14.42000007629395</v>
+        <v>14.57999992370605</v>
       </c>
       <c r="I37" t="n">
-        <v>2.080443817009344</v>
+        <v>2.057613179491319</v>
       </c>
       <c r="J37" t="n">
         <v>59</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>39.70000076293945</v>
+        <v>39.29999923706055</v>
       </c>
       <c r="I38" t="n">
-        <v>2.141057893362782</v>
+        <v>2.162849914761413</v>
       </c>
       <c r="J38" t="n">
         <v>59</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>30.04000091552734</v>
+        <v>29.44000053405762</v>
       </c>
       <c r="I39" t="n">
-        <v>2.829560499649134</v>
+        <v>2.887228208493675</v>
       </c>
       <c r="J39" t="n">
         <v>59</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5.5</v>
+        <v>5.389999866485596</v>
       </c>
       <c r="I40" t="n">
-        <v>3.636363636363637</v>
+        <v>3.710575231060341</v>
       </c>
       <c r="J40" t="n">
         <v>59</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>22.29999923706055</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="I41" t="n">
-        <v>4.484305086154855</v>
+        <v>4.504504349699816</v>
       </c>
       <c r="J41" t="n">
         <v>59</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>4.139999866485596</v>
+        <v>4.28000020980835</v>
       </c>
       <c r="I42" t="n">
-        <v>5.193236882456988</v>
+        <v>5.023364239732766</v>
       </c>
       <c r="J42" t="n">
         <v>59</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>18.40500068664551</v>
+        <v>18.23500061035156</v>
       </c>
       <c r="I43" t="n">
-        <v>4.292311711638328</v>
+        <v>4.332327795764023</v>
       </c>
       <c r="J43" t="n">
         <v>59</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>4.489999771118164</v>
+        <v>4.570000171661377</v>
       </c>
       <c r="I44" t="n">
-        <v>2.071269593335409</v>
+        <v>2.035010864478607</v>
       </c>
       <c r="J44" t="n">
         <v>59</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2.019999980926514</v>
+        <v>1.919999957084656</v>
       </c>
       <c r="I45" t="n">
-        <v>2.970297057749466</v>
+        <v>3.125000069849194</v>
       </c>
       <c r="J45" t="n">
         <v>59</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5.559999942779541</v>
+        <v>5.429999828338623</v>
       </c>
       <c r="I46" t="n">
-        <v>1.852518004676606</v>
+        <v>1.896869304902246</v>
       </c>
       <c r="J46" t="n">
         <v>59</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>5.078000068664551</v>
+        <v>4.966000080108643</v>
       </c>
       <c r="I47" t="n">
-        <v>3.741630512619658</v>
+        <v>3.826016853303058</v>
       </c>
       <c r="J47" t="n">
         <v>59</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9.904999732971191</v>
+        <v>9.725000381469727</v>
       </c>
       <c r="I48" t="n">
-        <v>4.361433736964003</v>
+        <v>4.442159208786708</v>
       </c>
       <c r="J48" t="n">
         <v>59</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>24.95999908447266</v>
+        <v>24.6200008392334</v>
       </c>
       <c r="I49" t="n">
-        <v>1.762820577480386</v>
+        <v>1.787164845660096</v>
       </c>
       <c r="J49" t="n">
         <v>59</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>6.449999809265137</v>
+        <v>6.510000228881836</v>
       </c>
       <c r="I50" t="n">
-        <v>7.286821920907129</v>
+        <v>7.219661804539254</v>
       </c>
       <c r="J50" t="n">
         <v>59</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>51.7400016784668</v>
+        <v>52.09999847412109</v>
       </c>
       <c r="I51" t="n">
-        <v>2.705836788912694</v>
+        <v>2.687140193862774</v>
       </c>
       <c r="J51" t="n">
         <v>59</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.875</v>
+        <v>2.844000101089478</v>
       </c>
       <c r="I52" t="n">
-        <v>10.43478260869565</v>
+        <v>10.54852283180567</v>
       </c>
       <c r="J52" t="n">
         <v>59</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>81.25</v>
+        <v>78.75</v>
       </c>
       <c r="I53" t="n">
-        <v>1.661538461538461</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="J53" t="n">
         <v>59</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>3.41100001335144</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="I54" t="n">
-        <v>4.983875676768713</v>
+        <v>4.970760123029561</v>
       </c>
       <c r="J54" t="n">
         <v>59</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>4.679999828338623</v>
+        <v>4.380000114440918</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8547008860510965</v>
+        <v>0.9132419852711756</v>
       </c>
       <c r="J55" t="n">
         <v>59</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>28.54999923706055</v>
+        <v>28.89999961853027</v>
       </c>
       <c r="I56" t="n">
-        <v>3.677758417019509</v>
+        <v>3.633218041036772</v>
       </c>
       <c r="J56" t="n">
         <v>59</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>17.11000061035156</v>
+        <v>17.22999954223633</v>
       </c>
       <c r="I57" t="n">
-        <v>2.220923357361541</v>
+        <v>2.205455659290626</v>
       </c>
       <c r="J57" t="n">
         <v>59</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>24.18000030517578</v>
+        <v>24.48999977111816</v>
       </c>
       <c r="I58" t="n">
-        <v>2.481389546846154</v>
+        <v>2.449979606400809</v>
       </c>
       <c r="J58" t="n">
         <v>59</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>30.5</v>
+        <v>30.85000038146973</v>
       </c>
       <c r="I59" t="n">
-        <v>1.147540983606557</v>
+        <v>1.134521866036118</v>
       </c>
       <c r="J59" t="n">
         <v>59</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>2.319999933242798</v>
+        <v>2.236000061035156</v>
       </c>
       <c r="I60" t="n">
-        <v>11.20689687419874</v>
+        <v>11.62790665934208</v>
       </c>
       <c r="J60" t="n">
         <v>59</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>10.10000038146973</v>
+        <v>9.939999580383301</v>
       </c>
       <c r="I61" t="n">
-        <v>3.465346403769827</v>
+        <v>3.521126909207611</v>
       </c>
       <c r="J61" t="n">
         <v>52</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>13.9399995803833</v>
+        <v>13.92000007629395</v>
       </c>
       <c r="I62" t="n">
-        <v>3.586800681856633</v>
+        <v>3.591954003301412</v>
       </c>
       <c r="J62" t="n">
         <v>52</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>6.420000076293945</v>
+        <v>6.489999771118164</v>
       </c>
       <c r="I63" t="n">
-        <v>3.426791236535292</v>
+        <v>3.389830628023214</v>
       </c>
       <c r="J63" t="n">
         <v>52</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>3.430000066757202</v>
+        <v>3.365000009536743</v>
       </c>
       <c r="I64" t="n">
-        <v>4.664722941281676</v>
+        <v>4.754829109852724</v>
       </c>
       <c r="J64" t="n">
         <v>45</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>18.76000022888184</v>
+        <v>19.31999969482422</v>
       </c>
       <c r="I65" t="n">
-        <v>3.251599107450321</v>
+        <v>3.157349946353351</v>
       </c>
       <c r="J65" t="n">
         <v>45</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>11.89999961853027</v>
+        <v>11.85000038146973</v>
       </c>
       <c r="I66" t="n">
-        <v>5.882353129742826</v>
+        <v>5.907172805619612</v>
       </c>
       <c r="J66" t="n">
         <v>45</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>8.649999618530273</v>
+        <v>8.409999847412109</v>
       </c>
       <c r="I67" t="n">
-        <v>5.901734364315953</v>
+        <v>6.070154688018085</v>
       </c>
       <c r="J67" t="n">
         <v>45</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>7.170000076293945</v>
+        <v>6.945000171661377</v>
       </c>
       <c r="I68" t="n">
-        <v>3.76569033649939</v>
+        <v>3.887688888788189</v>
       </c>
       <c r="J68" t="n">
         <v>45</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>4.554999828338623</v>
+        <v>4.53000020980835</v>
       </c>
       <c r="I69" t="n">
-        <v>7.68386417541662</v>
+        <v>7.726268957828755</v>
       </c>
       <c r="J69" t="n">
         <v>45</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>18.60000038146973</v>
+        <v>18.5</v>
       </c>
       <c r="I70" t="n">
-        <v>4.032257981818046</v>
+        <v>4.054054054054054</v>
       </c>
       <c r="J70" t="n">
         <v>45</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>10.19999980926514</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I71" t="n">
-        <v>4.215686353341016</v>
+        <v>4.174757204245461</v>
       </c>
       <c r="J71" t="n">
         <v>45</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>4</v>
+        <v>3.904999971389771</v>
       </c>
       <c r="I72" t="n">
-        <v>3.75</v>
+        <v>3.841229221484878</v>
       </c>
       <c r="J72" t="n">
         <v>45</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>11.5</v>
+        <v>11.53999996185303</v>
       </c>
       <c r="I73" t="n">
-        <v>1.714513043478261</v>
+        <v>1.708570196289149</v>
       </c>
       <c r="J73" t="n">
         <v>45</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>24.79999923706055</v>
+        <v>25</v>
       </c>
       <c r="I74" t="n">
-        <v>4.435484007419586</v>
+        <v>4.4</v>
       </c>
       <c r="J74" t="n">
         <v>45</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>35.79999923706055</v>
+        <v>36</v>
       </c>
       <c r="I75" t="n">
-        <v>1.312849189989509</v>
+        <v>1.305555555555555</v>
       </c>
       <c r="J75" t="n">
         <v>45</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>73.30000305175781</v>
+        <v>75.40000152587891</v>
       </c>
       <c r="I76" t="n">
-        <v>1.637107708102916</v>
+        <v>1.591511904131904</v>
       </c>
       <c r="J76" t="n">
         <v>45</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>22.25</v>
+        <v>22.14999961853027</v>
       </c>
       <c r="I77" t="n">
-        <v>1.213483146067416</v>
+        <v>1.218961646275258</v>
       </c>
       <c r="J77" t="n">
         <v>45</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>10.05000019073486</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="I78" t="n">
-        <v>3.78109445560333</v>
+        <v>3.762376095521527</v>
       </c>
       <c r="J78" t="n">
         <v>45</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>27.25</v>
+        <v>27.39999961853027</v>
       </c>
       <c r="I79" t="n">
-        <v>1.10091743119266</v>
+        <v>1.094890526192248</v>
       </c>
       <c r="J79" t="n">
         <v>45</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>5.940000057220459</v>
+        <v>5.909999847412109</v>
       </c>
       <c r="I80" t="n">
-        <v>2.69360266765502</v>
+        <v>2.707275873620561</v>
       </c>
       <c r="J80" t="n">
         <v>38</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>2.180000066757202</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="I81" t="n">
-        <v>2.981651284840964</v>
+        <v>3.037383028675626</v>
       </c>
       <c r="J81" t="n">
         <v>38</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>7.179999828338623</v>
+        <v>7.329999923706055</v>
       </c>
       <c r="I82" t="n">
-        <v>3.481894233663894</v>
+        <v>3.410641236045195</v>
       </c>
       <c r="J82" t="n">
         <v>38</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.279999971389771</v>
+        <v>1.340000033378601</v>
       </c>
       <c r="I83" t="n">
-        <v>5.468750122236091</v>
+        <v>5.223880466891178</v>
       </c>
       <c r="J83" t="n">
         <v>38</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>6.650000095367432</v>
+        <v>6.585000038146973</v>
       </c>
       <c r="I84" t="n">
-        <v>7.518796884654384</v>
+        <v>7.593014382741001</v>
       </c>
       <c r="J84" t="n">
         <v>31</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>16.71999931335449</v>
+        <v>16.44000053405762</v>
       </c>
       <c r="I85" t="n">
-        <v>3.887559968264091</v>
+        <v>3.953771161098443</v>
       </c>
       <c r="J85" t="n">
         <v>31</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>11.57999992370605</v>
+        <v>11.24499988555908</v>
       </c>
       <c r="I86" t="n">
-        <v>4.663212465956381</v>
+        <v>4.802134330774625</v>
       </c>
       <c r="J86" t="n">
         <v>31</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5.98199987411499</v>
+        <v>5.912000179290771</v>
       </c>
       <c r="I87" t="n">
-        <v>1.671681746980888</v>
+        <v>1.691474914873843</v>
       </c>
       <c r="J87" t="n">
         <v>31</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>8.119999885559082</v>
+        <v>8.159999847412109</v>
       </c>
       <c r="I88" t="n">
-        <v>1.97044337752455</v>
+        <v>1.96078435039117</v>
       </c>
       <c r="J88" t="n">
         <v>31</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>274.2999877929688</v>
+        <v>273.7999877929688</v>
       </c>
       <c r="I89" t="n">
-        <v>1.317900168019134</v>
+        <v>1.320306852143999</v>
       </c>
       <c r="J89" t="n">
         <v>31</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>26.29999923706055</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="I90" t="n">
-        <v>5.171102811606022</v>
+        <v>5.190839543500142</v>
       </c>
       <c r="J90" t="n">
         <v>31</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>12.52000045776367</v>
+        <v>12.14999961853027</v>
       </c>
       <c r="I91" t="n">
-        <v>4.672523790821753</v>
+        <v>4.814814965984045</v>
       </c>
       <c r="J91" t="n">
         <v>31</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>15.46000003814697</v>
+        <v>15.625</v>
       </c>
       <c r="I92" t="n">
-        <v>4.07503233147153</v>
+        <v>4.032</v>
       </c>
       <c r="J92" t="n">
         <v>31</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>94.66000366210938</v>
+        <v>93.90000152587891</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9507711442866267</v>
+        <v>0.9584664380990019</v>
       </c>
       <c r="J93" t="n">
         <v>31</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>62.0099983215332</v>
+        <v>59.63000106811523</v>
       </c>
       <c r="I94" t="n">
-        <v>2.775036359584041</v>
+        <v>2.885795688707658</v>
       </c>
       <c r="J94" t="n">
         <v>31</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>23.39999961853027</v>
+        <v>22.79999923706055</v>
       </c>
       <c r="I95" t="n">
-        <v>0.5982906080440067</v>
+        <v>0.6140351082662987</v>
       </c>
       <c r="J95" t="n">
         <v>24</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1.509999990463257</v>
+        <v>1.450000047683716</v>
       </c>
       <c r="I96" t="n">
-        <v>3.973509958870426</v>
+        <v>4.137930898405571</v>
       </c>
       <c r="J96" t="n">
         <v>24</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1.889999985694885</v>
+        <v>1.929999947547913</v>
       </c>
       <c r="I97" t="n">
-        <v>1.798941812557709</v>
+        <v>1.7616580789651</v>
       </c>
       <c r="J97" t="n">
         <v>10</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>23.93499946594238</v>
+        <v>23.6200008392334</v>
       </c>
       <c r="I98" t="n">
-        <v>1.086275353253964</v>
+        <v>1.10076202693496</v>
       </c>
       <c r="J98" t="n">
         <v>3</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>27.79999923706055</v>
+        <v>26.92000007629395</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3237410160789494</v>
+        <v>0.3343239217865197</v>
       </c>
       <c r="J99" t="n">
         <v>3</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>51.29999923706055</v>
+        <v>50.34999847412109</v>
       </c>
       <c r="I100" t="n">
-        <v>1.267056549058235</v>
+        <v>1.290963296322813</v>
       </c>
       <c r="J100" t="n">
         <v>-25</v>
@@ -5447,7 +5447,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5464,7 +5464,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5481,7 +5481,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5498,7 +5498,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5515,7 +5515,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5532,7 +5532,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5549,7 +5549,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5566,7 +5566,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5576,14 +5576,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5593,14 +5593,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5651,7 +5651,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5661,14 +5661,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5753,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5763,14 +5763,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5797,14 +5797,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5814,14 +5814,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5848,14 +5848,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5865,14 +5865,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5889,7 +5889,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5923,7 +5923,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5933,14 +5933,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5950,14 +5950,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5967,14 +5967,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5984,14 +5984,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6001,14 +6001,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6025,7 +6025,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6042,7 +6042,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6059,7 +6059,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6229,7 +6229,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6263,7 +6263,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6280,7 +6280,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6297,7 +6297,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6307,14 +6307,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6433,7 +6433,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -6569,7 +6569,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6586,7 +6586,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6603,7 +6603,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6637,7 +6637,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6647,14 +6647,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6671,7 +6671,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6688,7 +6688,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6773,7 +6773,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6790,7 +6790,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6875,7 +6875,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6885,14 +6885,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6909,7 +6909,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6926,7 +6926,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6943,7 +6943,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6953,14 +6953,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6977,7 +6977,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6994,7 +6994,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7011,7 +7011,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7028,7 +7028,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7045,7 +7045,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7062,7 +7062,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7079,7 +7079,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7096,7 +7096,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7113,7 +7113,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7130,7 +7130,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7147,7 +7147,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7164,7 +7164,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7181,7 +7181,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7198,7 +7198,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7215,7 +7215,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7232,7 +7232,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7266,7 +7266,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7283,7 +7283,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7300,7 +7300,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7317,7 +7317,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7334,7 +7334,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7351,7 +7351,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7368,7 +7368,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7385,7 +7385,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7402,7 +7402,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7419,7 +7419,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7429,14 +7429,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7453,7 +7453,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7470,7 +7470,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7487,7 +7487,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7504,7 +7504,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7521,7 +7521,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7538,7 +7538,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7555,7 +7555,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7572,7 +7572,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7582,14 +7582,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -7623,7 +7623,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7640,7 +7640,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -7657,7 +7657,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7674,7 +7674,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7691,7 +7691,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -7708,7 +7708,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7725,7 +7725,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -7742,7 +7742,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7752,14 +7752,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7776,7 +7776,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7793,7 +7793,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7810,7 +7810,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7827,7 +7827,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7844,7 +7844,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7861,7 +7861,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7878,7 +7878,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7895,7 +7895,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7912,7 +7912,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7929,7 +7929,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7946,7 +7946,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7963,7 +7963,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7997,7 +7997,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -8014,7 +8014,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -8031,7 +8031,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -8041,14 +8041,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -8058,14 +8058,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8082,7 +8082,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -8099,7 +8099,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -8116,7 +8116,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -8133,7 +8133,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8150,7 +8150,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8160,14 +8160,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8184,7 +8184,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8201,7 +8201,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8218,7 +8218,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8228,14 +8228,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8252,7 +8252,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8262,14 +8262,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8279,14 +8279,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8303,7 +8303,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8320,7 +8320,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8337,7 +8337,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8354,7 +8354,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8371,7 +8371,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8388,7 +8388,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8405,7 +8405,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8415,14 +8415,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8439,7 +8439,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8449,14 +8449,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8466,14 +8466,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8490,7 +8490,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8507,7 +8507,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8517,14 +8517,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -8541,7 +8541,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -8558,7 +8558,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -8592,7 +8592,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -8609,7 +8609,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -8626,7 +8626,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -8643,7 +8643,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -8660,7 +8660,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -8677,7 +8677,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -8687,14 +8687,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -8704,14 +8704,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -8721,14 +8721,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -8745,7 +8745,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -8762,7 +8762,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -8779,7 +8779,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -8796,7 +8796,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -8813,7 +8813,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -8823,14 +8823,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -8847,7 +8847,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -8857,14 +8857,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -8874,14 +8874,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -8898,7 +8898,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -8908,14 +8908,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -8925,14 +8925,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -8949,7 +8949,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -8966,7 +8966,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -8983,7 +8983,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -9017,7 +9017,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9163,14 +9163,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -9180,14 +9180,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -9197,14 +9197,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -9221,7 +9221,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -9238,7 +9238,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9306,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -9323,7 +9323,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -9340,7 +9340,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -9350,14 +9350,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -9367,14 +9367,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -9391,7 +9391,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -9435,14 +9435,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -9452,14 +9452,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -9469,14 +9469,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -9486,14 +9486,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -9510,7 +9510,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -9520,14 +9520,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -9537,14 +9537,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -9554,14 +9554,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -9595,7 +9595,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -9605,14 +9605,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -9622,14 +9622,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -9639,14 +9639,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -9656,14 +9656,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -9680,7 +9680,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -9690,14 +9690,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -9714,7 +9714,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -9731,7 +9731,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -9741,14 +9741,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -9758,14 +9758,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -9775,14 +9775,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -9799,7 +9799,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -9809,14 +9809,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -9833,7 +9833,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -9843,14 +9843,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -9867,7 +9867,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -9877,14 +9877,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -9894,14 +9894,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -9911,14 +9911,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -9928,14 +9928,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -9945,14 +9945,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -9962,14 +9962,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -9986,7 +9986,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -10003,7 +10003,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -10013,14 +10013,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -10030,14 +10030,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -10047,14 +10047,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -10071,7 +10071,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -10081,14 +10081,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -10098,14 +10098,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -10122,7 +10122,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -10132,14 +10132,14 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -10149,14 +10149,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -10166,14 +10166,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -10198,272 +10198,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0001469383</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1.945999979972839</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3.956834573095664</v>
-      </c>
-      <c r="I2" t="n">
-        <v>59</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0001469383</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-11-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1.945999979972839</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>3.956834573095664</v>
-      </c>
-      <c r="I3" t="n">
-        <v>248</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0001268561</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>11.89999961853027</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>5.882353129742826</v>
-      </c>
-      <c r="I4" t="n">
-        <v>45</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DATALOGIC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IT0004053440</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-07-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4.320000171661377</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>2.77777766739881</v>
-      </c>
-      <c r="I5" t="n">
-        <v>115</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TECHNOGYM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>IT0005162406</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>17.11000061035156</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>2.220923357361541</v>
-      </c>
-      <c r="I6" t="n">
-        <v>59</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10474,61 +10211,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CLASS EDITORI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ESI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>